--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/ILLINOIS_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/ILLINOIS_2023.xlsx
@@ -4416,7 +4416,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C226">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C379">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C389">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C879">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C881">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C882">
@@ -29526,7 +29526,7 @@
       </c>
       <c r="B1621" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1621">
